--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488192_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488192_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6643</v>
+        <v>1.826</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8218</v>
+        <v>1.3528</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8425</v>
+        <v>0.4732</v>
       </c>
       <c r="G2" t="n">
         <v>2.9888</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1202</v>
+        <v>0.282</v>
       </c>
       <c r="T2" t="n">
-        <v>2.119</v>
+        <v>0.6501</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0012</v>
+        <v>-0.3681</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2594</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1605</v>
+        <v>1.4795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7892</v>
+        <v>0.9851</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3713</v>
+        <v>0.4945</v>
       </c>
       <c r="G3" t="n">
         <v>0.3726</v>
@@ -688,13 +688,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3979</v>
+        <v>-0.079</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1244</v>
+        <v>-0.0012</v>
       </c>
       <c r="V3" t="n">
         <v>0.63</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7383999999999999</v>
+        <v>1.2533</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5934</v>
+        <v>-0.2017</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3318</v>
+        <v>1.4549</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0495</v>
@@ -766,13 +766,13 @@
         <v>1.297</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9538</v>
+        <v>-0.439</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9849</v>
+        <v>-0.5931</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0311</v>
+        <v>0.1542</v>
       </c>
       <c r="V4" t="n">
         <v>0.63</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0948</v>
+        <v>0.8854</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9623</v>
+        <v>1.5067</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8675</v>
+        <v>-0.6213</v>
       </c>
       <c r="G5" t="n">
         <v>3.4506</v>
@@ -844,13 +844,13 @@
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5034</v>
+        <v>-0.7129</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.149</v>
+        <v>-0.6047</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3544</v>
+        <v>-0.1082</v>
       </c>
       <c r="V5" t="n">
         <v>0.0005</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0725</v>
+        <v>-0.0233</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0498</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1053</v>
@@ -922,13 +922,13 @@
         <v>0.1853</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1281</v>
+        <v>-0.2574</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2476</v>
+        <v>1.0793</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3757</v>
+        <v>-1.3367</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.058</v>
+        <v>0.6847</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6558</v>
+        <v>2.4327</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4022</v>
+        <v>-1.748</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5259</v>
+        <v>2.6766</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4845</v>
+        <v>3.3495</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>-0.673</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.584</v>
+        <v>-1.9918</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1403</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4437</v>
+        <v>-1.075</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4019</v>
+        <v>-1.0539</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3132</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9112</v>
+        <v>-0.383</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5172</v>
+        <v>-0.6294</v>
       </c>
       <c r="W7" t="n">
-        <v>3.1466</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-0.6294</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9736</v>
+        <v>-0.3694</v>
       </c>
       <c r="E8" t="n">
-        <v>0.437</v>
+        <v>1.4003</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4106</v>
+        <v>-1.7697</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6847</v>
+        <v>-2.058</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4327</v>
+        <v>-0.6558</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.748</v>
+        <v>-1.4022</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6766</v>
+        <v>0.5259</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3495</v>
+        <v>0.4845</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.673</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9918</v>
+        <v>-2.584</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-1.1403</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.075</v>
+        <v>-1.4437</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7701</v>
+        <v>-0.6432</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3132</v>
+        <v>-1.1605</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4569</v>
+        <v>0.5173</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6294</v>
+        <v>2.5172</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.1466</v>
       </c>
       <c r="X8" t="n">
         <v>-0.6294</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3263</v>
+        <v>-1.962</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7429</v>
+        <v>-1.5263</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5834</v>
+        <v>-0.4356</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4357</v>
@@ -1156,13 +1156,13 @@
         <v>0.1853</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9242</v>
+        <v>0.2885</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0869</v>
+        <v>0.3034</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1627</v>
+        <v>-0.0149</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1338</v>
+        <v>-2.1529</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.416</v>
+        <v>-3.3613</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2822</v>
+        <v>1.2084</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3792</v>
@@ -1234,13 +1234,13 @@
         <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1251</v>
+        <v>-0.1443</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3867</v>
+        <v>-0.332</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2616</v>
+        <v>0.1878</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6294</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>G. VELASCO BENITEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4328</v>
+        <v>-3.4225</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0314</v>
+        <v>-2.4196</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4014</v>
+        <v>-1.0029</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8291</v>
+        <v>-1.8688</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7155</v>
+        <v>0.1358</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1136</v>
+        <v>-2.0046</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8635</v>
+        <v>-1.2628</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2107</v>
+        <v>0.0429</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6529</v>
+        <v>-1.3057</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9656</v>
+        <v>-0.606</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5048</v>
+        <v>0.0929</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4607</v>
+        <v>-0.6989</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0124</v>
+        <v>-0.3684</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1679</v>
+        <v>-0.2304</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1554</v>
+        <v>-0.138</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5177</v>
+        <v>-0.6294</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5177</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. VELASCO BENITEZ</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5942</v>
+        <v>-3.7698</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5175</v>
+        <v>-1.3684</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0767</v>
+        <v>-2.4014</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8688</v>
+        <v>-1.8291</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1358</v>
+        <v>-0.7155</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0046</v>
+        <v>-1.1136</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2628</v>
+        <v>-0.8635</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0429</v>
+        <v>-0.2107</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3057</v>
+        <v>-0.6529</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.606</v>
+        <v>-0.9656</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0929</v>
+        <v>-0.5048</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6989</v>
+        <v>-0.4607</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5402</v>
+        <v>-0.3494</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3283</v>
+        <v>-0.5049</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2119</v>
+        <v>0.1554</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6294</v>
+        <v>-2.5177</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6294</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2426</v>
+        <v>-4.4592</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2004</v>
+        <v>-2.4169</v>
       </c>
       <c r="F13" t="n">
         <v>-2.0422</v>
@@ -1468,10 +1468,10 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2782</v>
+        <v>-1.4947</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.915</v>
+        <v>-1.1316</v>
       </c>
       <c r="U13" t="n">
         <v>-0.3631</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.2459</v>
+        <v>-10.9723</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.366</v>
+        <v>-5.0923</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.879899999999999</v>
+        <v>-5.8797</v>
       </c>
       <c r="G14" t="n">
         <v>-6.305600000000001</v>
@@ -1546,13 +1546,13 @@
         <v>13.8967</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.9058</v>
+        <v>-4.632199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6259</v>
+        <v>-4.3523</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2800999999999998</v>
+        <v>-0.2797</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8871</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9733</v>
+        <v>5.961</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2512</v>
+        <v>2.7409</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7221</v>
+        <v>3.2202</v>
       </c>
       <c r="G15" t="n">
         <v>2.1979</v>
@@ -1624,13 +1624,13 @@
         <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9046</v>
+        <v>1.8923</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3656</v>
+        <v>0.1241</v>
       </c>
       <c r="U15" t="n">
-        <v>3.2702</v>
+        <v>1.7683</v>
       </c>
       <c r="V15" t="n">
         <v>0.9444</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>D. LARA CALDERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0159</v>
+        <v>4.1597</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3937</v>
+        <v>1.5142</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6221</v>
+        <v>2.6455</v>
       </c>
       <c r="G16" t="n">
-        <v>4.0532</v>
+        <v>3.1612</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0862</v>
+        <v>-0.473</v>
       </c>
       <c r="I16" t="n">
-        <v>6.1394</v>
+        <v>3.6343</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4477</v>
+        <v>3.7756</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1248</v>
+        <v>1.6392</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5725</v>
+        <v>2.1364</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3945</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9614</v>
+        <v>-2.1122</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5669</v>
+        <v>1.4979</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.297</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R16" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1485</v>
+        <v>0.7222</v>
       </c>
       <c r="T16" t="n">
-        <v>0.485</v>
+        <v>-0.1284</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6635</v>
+        <v>0.8505</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.63</v>
+        <v>1.5733</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3139</v>
+        <v>1.5727</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9439</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6462</v>
+        <v>3.6001</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8532</v>
+        <v>2.9041</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2069</v>
+        <v>0.696</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8495</v>
+        <v>4.0532</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3609</v>
+        <v>-2.0862</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4886</v>
+        <v>6.1394</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0983</v>
+        <v>4.4477</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9324</v>
+        <v>-0.1248</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1659</v>
+        <v>4.5725</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2488</v>
+        <v>-0.3945</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5715</v>
+        <v>-1.9614</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3227</v>
+        <v>1.5669</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4823</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9439</v>
+        <v>0.7328</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1254</v>
+        <v>-0.0046</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1816</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6294</v>
+        <v>0.3139</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2589</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. LARA CALDERA</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3007</v>
+        <v>3.1594</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0246</v>
+        <v>2.8739</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2761</v>
+        <v>0.2855</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1612</v>
+        <v>1.8495</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.473</v>
+        <v>1.3609</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6343</v>
+        <v>0.4886</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7756</v>
+        <v>2.0983</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6392</v>
+        <v>1.9324</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1364</v>
+        <v>0.1659</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.2488</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1122</v>
+        <v>-0.5715</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4979</v>
+        <v>0.3227</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4087</v>
+        <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1368</v>
+        <v>0.457</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.618</v>
+        <v>0.1461</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4812</v>
+        <v>0.3109</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5733</v>
+        <v>-0.6294</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5727</v>
+        <v>0.6294</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0005</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.762</v>
+        <v>1.8857</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2567</v>
+        <v>0.1587</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5054</v>
+        <v>1.727</v>
       </c>
       <c r="G19" t="n">
         <v>2.1316</v>
@@ -1936,13 +1936,13 @@
         <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>0.91</v>
+        <v>1.0337</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2537</v>
+        <v>0.1558</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6563</v>
+        <v>0.8779</v>
       </c>
       <c r="V19" t="n">
         <v>0.9439</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>J. CANDELA SOLO DE ZALDIVAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1505</v>
+        <v>0.1785</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2891</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1386</v>
+        <v>0.1138</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6042</v>
+        <v>-0.0015</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1004</v>
+        <v>0.152</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5038</v>
+        <v>-0.1536</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5899</v>
+        <v>0.0215</v>
       </c>
       <c r="K21" t="n">
         <v>0.0215</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0143</v>
+        <v>-0.023</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1219</v>
+        <v>0.1306</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1076</v>
+        <v>-0.1536</v>
       </c>
       <c r="P21" t="n">
         <v>0.1853</v>
@@ -2092,19 +2092,19 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2549</v>
+        <v>-0.0053</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5646</v>
+        <v>0.0432</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3096</v>
+        <v>-0.0485</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CANDELA SOLO DE ZALDIVAR</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0313</v>
+        <v>-0.0202</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0332</v>
+        <v>-0.0047</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0645</v>
+        <v>-0.0155</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0015</v>
+        <v>-0.6042</v>
       </c>
       <c r="H22" t="n">
-        <v>0.152</v>
+        <v>-0.1004</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1536</v>
+        <v>-0.5038</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0215</v>
+        <v>-0.5899</v>
       </c>
       <c r="K22" t="n">
         <v>0.0215</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.023</v>
+        <v>-0.0143</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1306</v>
+        <v>-0.1219</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1536</v>
+        <v>0.1076</v>
       </c>
       <c r="P22" t="n">
         <v>0.1853</v>
@@ -2170,19 +2170,19 @@
         <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1525</v>
+        <v>0.0843</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0547</v>
+        <v>0.2708</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0977</v>
+        <v>-0.1865</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>A. CABALLERO SOLANA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.768</v>
+        <v>-0.9036</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2585</v>
+        <v>-0.0447</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0265</v>
+        <v>-0.8589</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1833</v>
+        <v>-0.7068</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0021</v>
+        <v>-0.8374</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8187</v>
+        <v>0.1306</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2645</v>
+        <v>0.0215</v>
       </c>
       <c r="K23" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0215</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1659</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4478</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1007</v>
+        <v>-0.8589</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6529</v>
+        <v>0.1306</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3417</v>
+        <v>-0.1968</v>
       </c>
       <c r="T23" t="n">
-        <v>0.291</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0507</v>
+        <v>-0.1306</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. CABALLERO SOLANA</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0015</v>
+        <v>-1.0864</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1427</v>
+        <v>-0.0353</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8589</v>
+        <v>-1.0512</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7068</v>
+        <v>-1.1833</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8374</v>
+        <v>-2.0021</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1306</v>
+        <v>0.8187</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0215</v>
+        <v>0.2645</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0215</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-1.4478</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8589</v>
+        <v>-2.1007</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1306</v>
+        <v>0.6529</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2947</v>
+        <v>0.0233</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1641</v>
+        <v>-0.0028</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1306</v>
+        <v>0.0261</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1867</v>
+        <v>-6.0104</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5934</v>
+        <v>-4.6141</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5933</v>
+        <v>-1.3963</v>
       </c>
       <c r="G25" t="n">
         <v>-4.9139</v>
@@ -2404,13 +2404,13 @@
         <v>1.8529</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.014</v>
+        <v>0.1623</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2373</v>
+        <v>-0.258</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2233</v>
+        <v>0.4203</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11.2458</v>
+        <v>11.2459</v>
       </c>
       <c r="E26" t="n">
-        <v>5.8798</v>
+        <v>5.879800000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>5.365999999999999</v>
+        <v>5.366099999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>6.305800000000001</v>
+        <v>6.305800000000003</v>
       </c>
       <c r="H26" t="n">
         <v>-6.0207</v>
@@ -2461,7 +2461,7 @@
         <v>7.7612</v>
       </c>
       <c r="L26" t="n">
-        <v>4.184200000000001</v>
+        <v>4.184199999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-5.639699999999999</v>
@@ -2482,13 +2482,13 @@
         <v>12.0437</v>
       </c>
       <c r="S26" t="n">
-        <v>4.905600000000001</v>
+        <v>4.9058</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.2799999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>4.625699999999999</v>
+        <v>4.6258</v>
       </c>
       <c r="V26" t="n">
         <v>1.8871</v>
@@ -2497,7 +2497,7 @@
         <v>7.550800000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.6639</v>
+        <v>-5.663899999999999</v>
       </c>
     </row>
   </sheetData>
